--- a/EKG_Kalite_Yönetim_Sistemi/14_Çıkış Lojistiği ve Ambalaj/02_OLG2 - Ambalaj Kalitesi ve Boş Ambalaj/EKG-LOJ-FRM-02_ambalaj_test_raporu_ve_ambalaj_onay_formu.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/14_Çıkış Lojistiği ve Ambalaj/02_OLG2 - Ambalaj Kalitesi ve Boş Ambalaj/EKG-LOJ-FRM-02_ambalaj_test_raporu_ve_ambalaj_onay_formu.xlsx
@@ -858,7 +858,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-FRM-02&amp;C&amp;"Arial,Regular"&amp;11Ambalaj Test Raporu ve Ambalaj Onay Formu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 25.09.2026
+Revizyon nedeni: Test raporu ve ambalaj kartı, uygulanabilir test planı ve gerçek onay kanıtını kaydedecek iki kısa forma dönüştürüldü.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1012,7 +1013,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-FRM-02&amp;C&amp;"Arial,Regular"&amp;11Ambalaj Test Raporu ve Ambalaj Onay Formu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 25.09.2026
+Revizyon nedeni: Test raporu ve ambalaj kartı, uygulanabilir test planı ve gerçek onay kanıtını kaydedecek iki kısa forma dönüştürüldü.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>